--- a/setting/setting.xlsx
+++ b/setting/setting.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
-    <sheet name="20251201" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,9 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
-  <si>
-    <t>目录</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
+  <si>
+    <t>公司</t>
   </si>
   <si>
     <t>文件名称摘要</t>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>G21</t>
+  </si>
+  <si>
+    <t>`</t>
   </si>
 </sst>
 </file>
@@ -1279,8 +1282,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="5.66666666666667" customWidth="1"/>
     <col min="2" max="2" width="14.1111111111111" customWidth="1"/>
@@ -1429,6 +1432,11 @@
         <v>24</v>
       </c>
     </row>
+    <row r="15" spans="5:5">
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/setting/setting.xlsx
+++ b/setting/setting.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="27948" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,16 +32,16 @@
     <t>公司</t>
   </si>
   <si>
-    <t>文件名称摘要</t>
-  </si>
-  <si>
-    <t>表格名称</t>
+    <t>源数据excel文件</t>
+  </si>
+  <si>
+    <t>源数据sheet表格</t>
   </si>
   <si>
     <t>源数据地址</t>
   </si>
   <si>
-    <t>目标文件</t>
+    <t>目标excel文件</t>
   </si>
   <si>
     <t>目标地址</t>
@@ -1286,7 +1286,7 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="5.66666666666667" customWidth="1"/>
-    <col min="2" max="2" width="14.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="17.5555555555556" customWidth="1"/>
     <col min="3" max="3" width="27.6666666666667" customWidth="1"/>
     <col min="4" max="4" width="11.8888888888889" customWidth="1"/>
     <col min="5" max="5" width="32.1111111111111" customWidth="1"/>

--- a/setting/setting.xlsx
+++ b/setting/setting.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
